--- a/gauss_results_abel.xlsx
+++ b/gauss_results_abel.xlsx
@@ -485,319 +485,319 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.082416852529805</v>
+        <v>120.8597842653912</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>118.6987998238035</v>
+        <v>775.7610205737726</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>207.3529782768475</v>
+        <v>1114.50828984476</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>37.47033173737021</v>
+        <v>183.3383008498511</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>185.4212643963682</v>
+        <v>721.4679933602243</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>0.2945</v>
+        <v>0.186</v>
       </c>
       <c r="B3" t="n">
-        <v>5.704678463950043</v>
+        <v>127.85907828277</v>
       </c>
       <c r="C3" t="n">
-        <v>0.3875</v>
+        <v>0.217</v>
       </c>
       <c r="D3" t="n">
-        <v>113.8562287200438</v>
+        <v>794.3160415746672</v>
       </c>
       <c r="E3" t="n">
-        <v>0.3565</v>
+        <v>0.2015</v>
       </c>
       <c r="F3" t="n">
-        <v>197.6687345490978</v>
+        <v>1111.255263950049</v>
       </c>
       <c r="G3" t="n">
-        <v>0.341</v>
+        <v>0.1705</v>
       </c>
       <c r="H3" t="n">
-        <v>36.13670630719545</v>
+        <v>179.6858810934173</v>
       </c>
       <c r="I3" t="n">
-        <v>0.403</v>
+        <v>0.1705</v>
       </c>
       <c r="J3" t="n">
-        <v>175.005895489797</v>
+        <v>701.9316850726997</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>0.6045</v>
+        <v>0.372</v>
       </c>
       <c r="B4" t="n">
-        <v>4.90003812379519</v>
+        <v>122.8685671952483</v>
       </c>
       <c r="C4" t="n">
-        <v>0.775</v>
+        <v>0.434</v>
       </c>
       <c r="D4" t="n">
-        <v>95.81829116684227</v>
+        <v>733.7616410784917</v>
       </c>
       <c r="E4" t="n">
-        <v>0.7285</v>
+        <v>0.4185</v>
       </c>
       <c r="F4" t="n">
-        <v>167.713218391078</v>
+        <v>991.7366331003308</v>
       </c>
       <c r="G4" t="n">
-        <v>0.6820000000000001</v>
+        <v>0.341</v>
       </c>
       <c r="H4" t="n">
-        <v>32.15508334982868</v>
+        <v>160.8609253094546</v>
       </c>
       <c r="I4" t="n">
-        <v>0.806</v>
+        <v>0.3565</v>
       </c>
       <c r="J4" t="n">
-        <v>147.4122934328793</v>
+        <v>615.9117989819896</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>0.9145</v>
+        <v>0.5735</v>
       </c>
       <c r="B5" t="n">
-        <v>3.85926857196453</v>
+        <v>105.5859402431212</v>
       </c>
       <c r="C5" t="n">
-        <v>1.1625</v>
+        <v>0.6665</v>
       </c>
       <c r="D5" t="n">
-        <v>70.74914703525617</v>
+        <v>601.242072316624</v>
       </c>
       <c r="E5" t="n">
-        <v>1.1005</v>
+        <v>0.6355</v>
       </c>
       <c r="F5" t="n">
-        <v>126.6030033733927</v>
+        <v>789.1306021978895</v>
       </c>
       <c r="G5" t="n">
-        <v>1.0385</v>
+        <v>0.5115</v>
       </c>
       <c r="H5" t="n">
-        <v>26.11358591346979</v>
+        <v>131.5415724235429</v>
       </c>
       <c r="I5" t="n">
-        <v>1.209</v>
+        <v>0.5425</v>
       </c>
       <c r="J5" t="n">
-        <v>110.816035661493</v>
+        <v>486.4843614106036</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>1.2245</v>
+        <v>0.7595</v>
       </c>
       <c r="B6" t="n">
-        <v>2.787069524401065</v>
+        <v>83.05310594734706</v>
       </c>
       <c r="C6" t="n">
-        <v>1.55</v>
+        <v>0.8835</v>
       </c>
       <c r="D6" t="n">
-        <v>45.83266972443293</v>
+        <v>448.7562341892747</v>
       </c>
       <c r="E6" t="n">
-        <v>1.457</v>
+        <v>0.837</v>
       </c>
       <c r="F6" t="n">
-        <v>86.65319485445215</v>
+        <v>575.933494416866</v>
       </c>
       <c r="G6" t="n">
-        <v>1.3795</v>
+        <v>0.6819999999999999</v>
       </c>
       <c r="H6" t="n">
-        <v>19.70872768568173</v>
+        <v>98.25425183487678</v>
       </c>
       <c r="I6" t="n">
-        <v>1.612</v>
+        <v>0.713</v>
       </c>
       <c r="J6" t="n">
-        <v>74.34630673028204</v>
+        <v>357.3007876812174</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>1.5345</v>
+        <v>0.961</v>
       </c>
       <c r="B7" t="n">
-        <v>1.845558679053759</v>
+        <v>57.45331851670065</v>
       </c>
       <c r="C7" t="n">
-        <v>1.9375</v>
+        <v>1.1005</v>
       </c>
       <c r="D7" t="n">
-        <v>26.0501520506292</v>
+        <v>302.1815317445551</v>
       </c>
       <c r="E7" t="n">
-        <v>1.829</v>
+        <v>1.054</v>
       </c>
       <c r="F7" t="n">
-        <v>52.03203300480435</v>
+        <v>367.3027351894498</v>
       </c>
       <c r="G7" t="n">
-        <v>1.736</v>
+        <v>0.8525</v>
       </c>
       <c r="H7" t="n">
-        <v>13.47460539299431</v>
+        <v>67.03714876444083</v>
       </c>
       <c r="I7" t="n">
-        <v>2.0305</v>
+        <v>0.899</v>
       </c>
       <c r="J7" t="n">
-        <v>43.54615142581986</v>
+        <v>230.6979892535953</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>1.8445</v>
+        <v>1.147</v>
       </c>
       <c r="B8" t="n">
-        <v>1.120585941017417</v>
+        <v>36.99180028845092</v>
       </c>
       <c r="C8" t="n">
-        <v>2.325</v>
+        <v>1.333</v>
       </c>
       <c r="D8" t="n">
-        <v>12.99051981984257</v>
+        <v>176.4617505029797</v>
       </c>
       <c r="E8" t="n">
-        <v>2.201</v>
+        <v>1.271</v>
       </c>
       <c r="F8" t="n">
-        <v>27.79741525546518</v>
+        <v>208.8555372028993</v>
       </c>
       <c r="G8" t="n">
-        <v>2.077</v>
+        <v>1.023</v>
       </c>
       <c r="H8" t="n">
-        <v>8.625795020945631</v>
+        <v>41.77876265727118</v>
       </c>
       <c r="I8" t="n">
-        <v>2.4335</v>
+        <v>1.085</v>
       </c>
       <c r="J8" t="n">
-        <v>23.16764381402303</v>
+        <v>134.0850405986669</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>2.1545</v>
+        <v>1.3485</v>
       </c>
       <c r="B9" t="n">
-        <v>0.6238780941389697</v>
+        <v>20.59959350364831</v>
       </c>
       <c r="C9" t="n">
-        <v>2.7125</v>
+        <v>1.55</v>
       </c>
       <c r="D9" t="n">
-        <v>5.683605911252156</v>
+        <v>96.00800988010741</v>
       </c>
       <c r="E9" t="n">
-        <v>2.5575</v>
+        <v>1.4725</v>
       </c>
       <c r="F9" t="n">
-        <v>13.66022499880877</v>
+        <v>111.5738367424974</v>
       </c>
       <c r="G9" t="n">
-        <v>2.4335</v>
+        <v>1.1935</v>
       </c>
       <c r="H9" t="n">
-        <v>4.964747816610466</v>
+        <v>23.78326473207723</v>
       </c>
       <c r="I9" t="n">
-        <v>2.8365</v>
+        <v>1.2555</v>
       </c>
       <c r="J9" t="n">
-        <v>11.00023187048244</v>
+        <v>74.34174133291457</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>2.4645</v>
+        <v>1.5345</v>
       </c>
       <c r="B10" t="n">
-        <v>0.3184868899659092</v>
+        <v>10.85649312612534</v>
       </c>
       <c r="C10" t="n">
-        <v>3.1</v>
+        <v>1.767</v>
       </c>
       <c r="D10" t="n">
-        <v>2.181737743151185</v>
+        <v>47.12600697909777</v>
       </c>
       <c r="E10" t="n">
-        <v>2.9295</v>
+        <v>1.6895</v>
       </c>
       <c r="F10" t="n">
-        <v>5.804983272983746</v>
+        <v>50.84912629958902</v>
       </c>
       <c r="G10" t="n">
-        <v>2.7745</v>
+        <v>1.364</v>
       </c>
       <c r="H10" t="n">
-        <v>2.695698230955572</v>
+        <v>12.36696763021094</v>
       </c>
       <c r="I10" t="n">
-        <v>3.2395</v>
+        <v>1.4415</v>
       </c>
       <c r="J10" t="n">
-        <v>4.661328330704203</v>
+        <v>35.32065296638601</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>2.7745</v>
+        <v>1.736</v>
       </c>
       <c r="B11" t="n">
-        <v>0.1490804307830987</v>
+        <v>4.866723657908453</v>
       </c>
       <c r="C11" t="n">
-        <v>3.503</v>
+        <v>1.9995</v>
       </c>
       <c r="D11" t="n">
-        <v>0.701576204408081</v>
+        <v>19.61243937972875</v>
       </c>
       <c r="E11" t="n">
-        <v>3.3015</v>
+        <v>1.9065</v>
       </c>
       <c r="F11" t="n">
-        <v>2.194782541522529</v>
+        <v>20.66210804270964</v>
       </c>
       <c r="G11" t="n">
-        <v>3.131</v>
+        <v>1.55</v>
       </c>
       <c r="H11" t="n">
-        <v>1.306200743860224</v>
+        <v>5.464960466180924</v>
       </c>
       <c r="I11" t="n">
-        <v>3.658</v>
+        <v>1.6275</v>
       </c>
       <c r="J11" t="n">
-        <v>1.694244873141916</v>
+        <v>15.10606679926364</v>
       </c>
     </row>
   </sheetData>
